--- a/results/followers_ads/estimates/followers_ads_b1_estimates.xlsx
+++ b/results/followers_ads/estimates/followers_ads_b1_estimates.xlsx
@@ -401,10 +401,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.001199292879202413</v>
+        <v>-0.001199292879202387</v>
       </c>
       <c r="C3">
-        <v>0.003570403332312873</v>
+        <v>0.003570403332313772</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
